--- a/results/rna_analysis/W281PvW281X_significant_genes.xlsx
+++ b/results/rna_analysis/W281PvW281X_significant_genes.xlsx
@@ -396,19 +396,19 @@
         <v>18.33242245713327</v>
       </c>
       <c r="B2">
-        <v>-3.751824084002779</v>
+        <v>-3.751824083998134</v>
       </c>
       <c r="C2">
-        <v>1.067077871072954</v>
+        <v>1.067077871548172</v>
       </c>
       <c r="D2">
-        <v>-3.515979654071821</v>
+        <v>-3.515979652501644</v>
       </c>
       <c r="E2">
-        <v>0.0004381345582284805</v>
+        <v>0.0004381345608196158</v>
       </c>
       <c r="F2">
-        <v>0.0219502512119103</v>
+        <v>0.02195025134172446</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -421,19 +421,19 @@
         <v>17.17114134123517</v>
       </c>
       <c r="B3">
-        <v>-3.66659128113211</v>
+        <v>-3.66659128113591</v>
       </c>
       <c r="C3">
-        <v>1.123765399903723</v>
+        <v>1.123765400389139</v>
       </c>
       <c r="D3">
-        <v>-3.2627728896496</v>
+        <v>-3.262772888243611</v>
       </c>
       <c r="E3">
-        <v>0.001103278959104028</v>
+        <v>0.00110327896457722</v>
       </c>
       <c r="F3">
-        <v>0.04451362840331719</v>
+        <v>0.04451362862414222</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -446,19 +446,19 @@
         <v>15.61412819416508</v>
       </c>
       <c r="B4">
-        <v>-7.348821098742158</v>
+        <v>-7.348821098742264</v>
       </c>
       <c r="C4">
-        <v>1.759343900358457</v>
+        <v>1.759343900769818</v>
       </c>
       <c r="D4">
-        <v>-4.177023660493479</v>
+        <v>-4.17702365951689</v>
       </c>
       <c r="E4">
-        <v>2.953483139286804E-05</v>
+        <v>2.953483151962431E-05</v>
       </c>
       <c r="F4">
-        <v>0.002234309994870467</v>
+        <v>0.002234310004459579</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -471,19 +471,19 @@
         <v>14.5481123098746</v>
       </c>
       <c r="B5">
-        <v>-4.041081772909852</v>
+        <v>-4.041081772914134</v>
       </c>
       <c r="C5">
-        <v>1.214243188941157</v>
+        <v>1.214243189535224</v>
       </c>
       <c r="D5">
-        <v>-3.328066247119533</v>
+        <v>-3.328066245494808</v>
       </c>
       <c r="E5">
-        <v>0.0008745106821882156</v>
+        <v>0.0008745106872884688</v>
       </c>
       <c r="F5">
-        <v>0.03769614422081967</v>
+        <v>0.03769614444066818</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -493,22 +493,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>14.49672952097074</v>
+        <v>14.49672952097073</v>
       </c>
       <c r="B6">
-        <v>-4.846024589366339</v>
+        <v>-4.846024589481507</v>
       </c>
       <c r="C6">
-        <v>1.492287697096823</v>
+        <v>1.492287697626307</v>
       </c>
       <c r="D6">
-        <v>-3.247379576199721</v>
+        <v>-3.247379575124683</v>
       </c>
       <c r="E6">
-        <v>0.001164729414281823</v>
+        <v>0.001164729418681731</v>
       </c>
       <c r="F6">
-        <v>0.04637462115285259</v>
+        <v>0.04637462132803839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -518,22 +518,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>280.068565570798</v>
+        <v>280.0685655707981</v>
       </c>
       <c r="B7">
-        <v>-2.348480856807488</v>
+        <v>-2.348480856807285</v>
       </c>
       <c r="C7">
-        <v>0.3160135944977656</v>
+        <v>0.3160135945593012</v>
       </c>
       <c r="D7">
-        <v>-7.431581734766454</v>
+        <v>-7.431581733318701</v>
       </c>
       <c r="E7">
-        <v>1.073066611941391E-13</v>
+        <v>1.073066623688699E-13</v>
       </c>
       <c r="F7">
-        <v>3.454361242270904E-11</v>
+        <v>3.454361280087236E-11</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>50.71433080960004</v>
       </c>
       <c r="B8">
-        <v>-2.405832699380725</v>
+        <v>-2.405832699372014</v>
       </c>
       <c r="C8">
-        <v>0.6420404542867939</v>
+        <v>0.6420404545925169</v>
       </c>
       <c r="D8">
-        <v>-3.747166838658519</v>
+        <v>-3.747166836860648</v>
       </c>
       <c r="E8">
-        <v>0.0001788431396174391</v>
+        <v>0.0001788431408988184</v>
       </c>
       <c r="F8">
-        <v>0.01040729500927636</v>
+        <v>0.01040729508384278</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -571,19 +571,19 @@
         <v>234.2329908357457</v>
       </c>
       <c r="B9">
-        <v>-3.244344308775438</v>
+        <v>-3.244344308781766</v>
       </c>
       <c r="C9">
-        <v>0.4308205015798405</v>
+        <v>0.4308205016630455</v>
       </c>
       <c r="D9">
-        <v>-7.530617268394296</v>
+        <v>-7.530617266954581</v>
       </c>
       <c r="E9">
-        <v>5.050101268527379E-14</v>
+        <v>5.050101324214355E-14</v>
       </c>
       <c r="F9">
-        <v>1.736546186200437E-11</v>
+        <v>1.736546205349164E-11</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -593,22 +593,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>394.3484758976949</v>
+        <v>394.3484758976948</v>
       </c>
       <c r="B10">
-        <v>-2.031192063172644</v>
+        <v>-2.031192063176096</v>
       </c>
       <c r="C10">
-        <v>0.2924267772238744</v>
+        <v>0.2924267772561436</v>
       </c>
       <c r="D10">
-        <v>-6.945985188003545</v>
+        <v>-6.945985187248864</v>
       </c>
       <c r="E10">
-        <v>3.758282031156084E-12</v>
+        <v>3.758282051249966E-12</v>
       </c>
       <c r="F10">
-        <v>1.072883153422482E-09</v>
+        <v>1.072883159158717E-09</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -621,19 +621,19 @@
         <v>13.41473163768618</v>
       </c>
       <c r="B11">
-        <v>-7.130050653131395</v>
+        <v>-7.130050653131134</v>
       </c>
       <c r="C11">
-        <v>1.81160945934201</v>
+        <v>1.811609459811322</v>
       </c>
       <c r="D11">
-        <v>-3.935754815345843</v>
+        <v>-3.935754814326109</v>
       </c>
       <c r="E11">
-        <v>8.293561278046207E-05</v>
+        <v>8.293561313265462E-05</v>
       </c>
       <c r="F11">
-        <v>0.005389071801705498</v>
+        <v>0.005389071765908727</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -643,22 +643,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>153.1933606103265</v>
+        <v>153.1933606103264</v>
       </c>
       <c r="B12">
-        <v>-2.527252890702007</v>
+        <v>-2.527252890675737</v>
       </c>
       <c r="C12">
-        <v>0.4575573920675486</v>
+        <v>0.4575573922047158</v>
       </c>
       <c r="D12">
-        <v>-5.523357144952237</v>
+        <v>-5.523357143239026</v>
       </c>
       <c r="E12">
-        <v>3.325827192335826E-08</v>
+        <v>3.325827224780023E-08</v>
       </c>
       <c r="F12">
-        <v>5.241642231254275E-06</v>
+        <v>5.241642282387682E-06</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -668,22 +668,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>92.9930111803283</v>
+        <v>92.99301118032828</v>
       </c>
       <c r="B13">
-        <v>-2.215181330772724</v>
+        <v>-2.21518133077568</v>
       </c>
       <c r="C13">
-        <v>0.455781502092717</v>
+        <v>0.4557815022935712</v>
       </c>
       <c r="D13">
-        <v>-4.860182610750409</v>
+        <v>-4.860182608615104</v>
       </c>
       <c r="E13">
-        <v>1.172775241224156E-06</v>
+        <v>1.172775253873955E-06</v>
       </c>
       <c r="F13">
-        <v>0.0001344249196948597</v>
+        <v>0.000134424921144795</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -696,19 +696,19 @@
         <v>31.77454921214384</v>
       </c>
       <c r="B14">
-        <v>-3.145509846468661</v>
+        <v>-3.145509846488362</v>
       </c>
       <c r="C14">
-        <v>0.7811029685230075</v>
+        <v>0.7811029689073943</v>
       </c>
       <c r="D14">
-        <v>-4.027010488023781</v>
+        <v>-4.027010486067281</v>
       </c>
       <c r="E14">
-        <v>5.649051368237679E-05</v>
+        <v>5.649051415225312E-05</v>
       </c>
       <c r="F14">
-        <v>0.003902746447554159</v>
+        <v>0.003902746480016391</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -721,19 +721,19 @@
         <v>271.5132381997524</v>
       </c>
       <c r="B15">
-        <v>-2.500496843111989</v>
+        <v>-2.500496843113184</v>
       </c>
       <c r="C15">
-        <v>0.3098440630239594</v>
+        <v>0.3098440630892248</v>
       </c>
       <c r="D15">
-        <v>-8.070178330054469</v>
+        <v>-8.070178328358429</v>
       </c>
       <c r="E15">
-        <v>7.019556533422262E-16</v>
+        <v>7.019556630934463E-16</v>
       </c>
       <c r="F15">
-        <v>3.034454010019395E-13</v>
+        <v>3.034454052172526E-13</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -743,22 +743,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>52.62494723659393</v>
+        <v>52.62494723659392</v>
       </c>
       <c r="B16">
-        <v>-2.541370448346052</v>
+        <v>-2.541370448337564</v>
       </c>
       <c r="C16">
-        <v>0.6539844101399719</v>
+        <v>0.653984410428602</v>
       </c>
       <c r="D16">
-        <v>-3.885980168551913</v>
+        <v>-3.885980166823893</v>
       </c>
       <c r="E16">
-        <v>0.0001019178269490016</v>
+        <v>0.0001019178276740763</v>
       </c>
       <c r="F16">
-        <v>0.006371969924538818</v>
+        <v>0.006371969969870971</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         <v>31.69468166954135</v>
       </c>
       <c r="B17">
-        <v>-2.605572027335001</v>
+        <v>-2.60557202733209</v>
       </c>
       <c r="C17">
-        <v>0.742244029720181</v>
+        <v>0.7422440301075112</v>
       </c>
       <c r="D17">
-        <v>-3.510398094164903</v>
+        <v>-3.510398092329126</v>
       </c>
       <c r="E17">
-        <v>0.000447436274306063</v>
+        <v>0.000447436277395486</v>
       </c>
       <c r="F17">
-        <v>0.02226811133157131</v>
+        <v>0.02226811131782453</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -796,19 +796,19 @@
         <v>14.27997553770204</v>
       </c>
       <c r="B18">
-        <v>-7.218388667684646</v>
+        <v>-7.218388667686919</v>
       </c>
       <c r="C18">
-        <v>1.788194632750165</v>
+        <v>1.788194633194914</v>
       </c>
       <c r="D18">
-        <v>-4.036690713349855</v>
+        <v>-4.036690712347145</v>
       </c>
       <c r="E18">
-        <v>5.421045988899984E-05</v>
+        <v>5.421046012059469E-05</v>
       </c>
       <c r="F18">
-        <v>0.003779743124979573</v>
+        <v>0.003779743141127178</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -821,19 +821,19 @@
         <v>64.29246328616226</v>
       </c>
       <c r="B19">
-        <v>-2.762078435270761</v>
+        <v>-2.76207843525993</v>
       </c>
       <c r="C19">
-        <v>0.5644826740824364</v>
+        <v>0.5644826743381662</v>
       </c>
       <c r="D19">
-        <v>-4.893114637682201</v>
+        <v>-4.893114635446267</v>
       </c>
       <c r="E19">
-        <v>9.925255348368829E-07</v>
+        <v>9.925255461175781E-07</v>
       </c>
       <c r="F19">
-        <v>0.0001155147026314003</v>
+        <v>0.0001155147039442997</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>38.27306168710138</v>
       </c>
       <c r="B20">
-        <v>-4.387899628377019</v>
+        <v>-4.387899628388919</v>
       </c>
       <c r="C20">
-        <v>0.8300609082912472</v>
+        <v>0.8300609085889467</v>
       </c>
       <c r="D20">
-        <v>-5.286238135716923</v>
+        <v>-5.286238133835362</v>
       </c>
       <c r="E20">
-        <v>1.248573355942101E-07</v>
+        <v>1.248573368778041E-07</v>
       </c>
       <c r="F20">
-        <v>1.799134750038475E-05</v>
+        <v>1.799134768534453E-05</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -868,22 +868,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>84.94901563053932</v>
+        <v>84.94901563053929</v>
       </c>
       <c r="B21">
-        <v>-2.128955813522029</v>
+        <v>-2.128955813522302</v>
       </c>
       <c r="C21">
-        <v>0.5406539101492582</v>
+        <v>0.5406539103588641</v>
       </c>
       <c r="D21">
-        <v>-3.937742377437516</v>
+        <v>-3.937742375911399</v>
       </c>
       <c r="E21">
-        <v>8.225183317993639E-05</v>
+        <v>8.225183370291397E-05</v>
       </c>
       <c r="F21">
-        <v>0.005387317039014881</v>
+        <v>0.00538731707326878</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -893,22 +893,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>95.41727013008604</v>
+        <v>95.41727013008602</v>
       </c>
       <c r="B22">
-        <v>-2.250519701819045</v>
+        <v>-2.250519701816095</v>
       </c>
       <c r="C22">
-        <v>0.4460483119448196</v>
+        <v>0.4460483121391403</v>
       </c>
       <c r="D22">
-        <v>-5.045461761768657</v>
+        <v>-5.04546175956399</v>
       </c>
       <c r="E22">
-        <v>4.524273733007499E-07</v>
+        <v>4.524273785179128E-07</v>
       </c>
       <c r="F22">
-        <v>5.752290889109535E-05</v>
+        <v>5.752290955442034E-05</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -918,22 +918,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>479.9442533683851</v>
+        <v>479.944253368385</v>
       </c>
       <c r="B23">
-        <v>-3.085027022858741</v>
+        <v>-3.085027022858499</v>
       </c>
       <c r="C23">
-        <v>0.2435700961745042</v>
+        <v>0.2435700961885304</v>
       </c>
       <c r="D23">
-        <v>-12.66586937933667</v>
+        <v>-12.66586937860631</v>
       </c>
       <c r="E23">
-        <v>9.140210384063085E-37</v>
+        <v>9.140210469137613E-37</v>
       </c>
       <c r="F23">
-        <v>1.728642288885931E-33</v>
+        <v>1.728642304975651E-33</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -946,19 +946,19 @@
         <v>204.392042758006</v>
       </c>
       <c r="B24">
-        <v>-2.349573106017128</v>
+        <v>-2.349573106002255</v>
       </c>
       <c r="C24">
-        <v>0.352448337709625</v>
+        <v>0.3524483378101861</v>
       </c>
       <c r="D24">
-        <v>-6.666432650202745</v>
+        <v>-6.666432648258469</v>
       </c>
       <c r="E24">
-        <v>2.620958786862136E-11</v>
+        <v>2.620958821566733E-11</v>
       </c>
       <c r="F24">
-        <v>6.294461340511765E-09</v>
+        <v>6.294461423857884E-09</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -971,19 +971,19 @@
         <v>207.0568701771583</v>
       </c>
       <c r="B25">
-        <v>-3.163896076682</v>
+        <v>-3.163896076681071</v>
       </c>
       <c r="C25">
-        <v>0.3299805919862145</v>
+        <v>0.3299805920799677</v>
       </c>
       <c r="D25">
-        <v>-9.588127767266315</v>
+        <v>-9.588127764539349</v>
       </c>
       <c r="E25">
-        <v>8.969782994603132E-22</v>
+        <v>8.969783231629894E-22</v>
       </c>
       <c r="F25">
-        <v>6.785640835417269E-19</v>
+        <v>6.785641014728015E-19</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -996,19 +996,19 @@
         <v>64.82384083012745</v>
       </c>
       <c r="B26">
-        <v>-2.722180007294146</v>
+        <v>-2.722180007293595</v>
       </c>
       <c r="C26">
-        <v>0.5491031831045129</v>
+        <v>0.549103183352319</v>
       </c>
       <c r="D26">
-        <v>-4.957501779362336</v>
+        <v>-4.957501777124051</v>
       </c>
       <c r="E26">
-        <v>7.140538857659884E-07</v>
+        <v>7.140538939896639E-07</v>
       </c>
       <c r="F26">
-        <v>8.71260910616081E-05</v>
+        <v>8.712609206502915E-05</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1018,22 +1018,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>47.60595405211423</v>
+        <v>47.60595405211421</v>
       </c>
       <c r="B27">
-        <v>-3.854656693198073</v>
+        <v>-3.854656693191713</v>
       </c>
       <c r="C27">
-        <v>0.7101458568233141</v>
+        <v>0.7101458571092338</v>
       </c>
       <c r="D27">
-        <v>-5.427978852740276</v>
+        <v>-5.427978850545901</v>
       </c>
       <c r="E27">
-        <v>5.699579086005088E-08</v>
+        <v>5.699579156062114E-08</v>
       </c>
       <c r="F27">
-        <v>8.623463157125699E-06</v>
+        <v>8.623463263121979E-06</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1043,22 +1043,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>84.30109023224844</v>
+        <v>84.30109023224841</v>
       </c>
       <c r="B28">
-        <v>-4.716465911505053</v>
+        <v>-4.716465911510535</v>
       </c>
       <c r="C28">
-        <v>0.6048212277855133</v>
+        <v>0.6048212279639521</v>
       </c>
       <c r="D28">
-        <v>-7.798115699037014</v>
+        <v>-7.798115696745421</v>
       </c>
       <c r="E28">
-        <v>6.283838489000017E-15</v>
+        <v>6.28383860308325E-15</v>
       </c>
       <c r="F28">
-        <v>2.501959903646586E-12</v>
+        <v>2.501959949069725E-12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>1700.86414784024</v>
+        <v>1700.864147840239</v>
       </c>
       <c r="B29">
-        <v>-2.530007856493893</v>
+        <v>-2.530007856494507</v>
       </c>
       <c r="C29">
-        <v>0.1610668891241865</v>
+        <v>0.1610668890514344</v>
       </c>
       <c r="D29">
-        <v>-15.70780853998611</v>
+        <v>-15.70780854708496</v>
       </c>
       <c r="E29">
-        <v>1.337221013351914E-55</v>
+        <v>1.33722086364247E-55</v>
       </c>
       <c r="F29">
-        <v>6.744051310671485E-52</v>
+        <v>6.744050555636856E-52</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>30.3834807913288</v>
+        <v>30.38348079132879</v>
       </c>
       <c r="B30">
-        <v>-2.76970035220349</v>
+        <v>-2.769700352206796</v>
       </c>
       <c r="C30">
-        <v>0.7889908411866856</v>
+        <v>0.7889908415725236</v>
       </c>
       <c r="D30">
-        <v>-3.510434098370151</v>
+        <v>-3.510434096657644</v>
       </c>
       <c r="E30">
-        <v>0.0004473756867766549</v>
+        <v>0.0004473756896582638</v>
       </c>
       <c r="F30">
-        <v>0.02226811133157131</v>
+        <v>0.02226811131782453</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1118,22 +1118,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>16.44604556453897</v>
+        <v>16.44604556453896</v>
       </c>
       <c r="B31">
-        <v>-7.425256090416625</v>
+        <v>-7.425256090414938</v>
       </c>
       <c r="C31">
-        <v>1.823260430719461</v>
+        <v>1.823260431118686</v>
       </c>
       <c r="D31">
-        <v>-4.072515349596333</v>
+        <v>-4.072515348703681</v>
       </c>
       <c r="E31">
-        <v>4.650813412485207E-05</v>
+        <v>4.650813430315257E-05</v>
       </c>
       <c r="F31">
-        <v>0.00333491975975835</v>
+        <v>0.003334919772543594</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1146,19 +1146,19 @@
         <v>14.45358521415213</v>
       </c>
       <c r="B32">
-        <v>-7.242320080508166</v>
+        <v>-7.242320080501556</v>
       </c>
       <c r="C32">
-        <v>1.786610853928329</v>
+        <v>1.786610854368519</v>
       </c>
       <c r="D32">
-        <v>-4.053663988766239</v>
+        <v>-4.053663987763787</v>
       </c>
       <c r="E32">
-        <v>5.042162517201523E-05</v>
+        <v>5.042162538818669E-05</v>
       </c>
       <c r="F32">
-        <v>0.003581592435927655</v>
+        <v>0.003581592451282933</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1168,22 +1168,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>51.95738916891618</v>
+        <v>51.95738916891617</v>
       </c>
       <c r="B33">
-        <v>-2.314244546353229</v>
+        <v>-2.314244546330763</v>
       </c>
       <c r="C33">
-        <v>0.6446634966166489</v>
+        <v>0.6446634969126733</v>
       </c>
       <c r="D33">
-        <v>-3.589848903340966</v>
+        <v>-3.589848901657686</v>
       </c>
       <c r="E33">
-        <v>0.000330869694657292</v>
+        <v>0.0003308696967938594</v>
       </c>
       <c r="F33">
-        <v>0.01726227062125803</v>
+        <v>0.01726227073272791</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1193,22 +1193,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>37.83297723219227</v>
+        <v>37.83297723219226</v>
       </c>
       <c r="B34">
-        <v>-2.510658288400529</v>
+        <v>-2.510658288382828</v>
       </c>
       <c r="C34">
-        <v>0.7415023161410693</v>
+        <v>0.7415023165004883</v>
       </c>
       <c r="D34">
-        <v>-3.385907547081595</v>
+        <v>-3.385907545416515</v>
       </c>
       <c r="E34">
-        <v>0.0007094328025016199</v>
+        <v>0.0007094328068060807</v>
       </c>
       <c r="F34">
-        <v>0.032136881143262</v>
+        <v>0.0321368813382515</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         <v>204.0704846395699</v>
       </c>
       <c r="B35">
-        <v>-4.971526460981821</v>
+        <v>-4.971526460977638</v>
       </c>
       <c r="C35">
-        <v>0.4154122076219212</v>
+        <v>0.4154122077050388</v>
       </c>
       <c r="D35">
-        <v>-11.96769466511815</v>
+        <v>-11.96769466271353</v>
       </c>
       <c r="E35">
-        <v>5.2466191221405E-33</v>
+        <v>5.24661927416653E-33</v>
       </c>
       <c r="F35">
-        <v>6.615112276498813E-30</v>
+        <v>6.6151124681783E-30</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1246,19 +1246,19 @@
         <v>328.5220214172719</v>
       </c>
       <c r="B36">
-        <v>-2.967163615867638</v>
+        <v>-2.967163615865459</v>
       </c>
       <c r="C36">
-        <v>0.2830741944275924</v>
+        <v>0.2830741944767785</v>
       </c>
       <c r="D36">
-        <v>-10.48192902877485</v>
+        <v>-10.48192902694585</v>
       </c>
       <c r="E36">
-        <v>1.045883436599598E-25</v>
+        <v>1.045883456830026E-25</v>
       </c>
       <c r="F36">
-        <v>1.130301171125137E-22</v>
+        <v>1.13030119298845E-22</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1268,22 +1268,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>68.63766075995689</v>
+        <v>68.63766075995687</v>
       </c>
       <c r="B37">
-        <v>-2.564671536919131</v>
+        <v>-2.564671536919668</v>
       </c>
       <c r="C37">
-        <v>0.5720682862614538</v>
+        <v>0.5720682865171931</v>
       </c>
       <c r="D37">
-        <v>-4.483156291846936</v>
+        <v>-4.483156289843709</v>
       </c>
       <c r="E37">
-        <v>7.354702136070384E-06</v>
+        <v>7.354702205141277E-06</v>
       </c>
       <c r="F37">
-        <v>0.0006681248447073982</v>
+        <v>0.0006681248474692716</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1296,19 +1296,19 @@
         <v>19.25918706690576</v>
       </c>
       <c r="B38">
-        <v>-4.688812202070401</v>
+        <v>-4.688812202156463</v>
       </c>
       <c r="C38">
-        <v>1.378292304288445</v>
+        <v>1.378292304718169</v>
       </c>
       <c r="D38">
-        <v>-3.40189971857315</v>
+        <v>-3.401899717574947</v>
       </c>
       <c r="E38">
-        <v>0.0006691918821524982</v>
+        <v>0.0006691918845966664</v>
       </c>
       <c r="F38">
-        <v>0.03049660595472077</v>
+        <v>0.03049660606610712</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>240.9890035132995</v>
+        <v>240.9890035132994</v>
       </c>
       <c r="B39">
-        <v>-4.618203061916668</v>
+        <v>-4.618203061918424</v>
       </c>
       <c r="C39">
-        <v>0.3894894286421975</v>
+        <v>0.3894894287104701</v>
       </c>
       <c r="D39">
-        <v>-11.85706908147989</v>
+        <v>-11.857069079406</v>
       </c>
       <c r="E39">
-        <v>1.977776362452969E-32</v>
+        <v>1.977776411428076E-32</v>
       </c>
       <c r="F39">
-        <v>2.301827412608724E-29</v>
+        <v>2.301827469608215E-29</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1346,19 +1346,19 @@
         <v>11.28116861883987</v>
       </c>
       <c r="B40">
-        <v>-6.879977367909627</v>
+        <v>-6.879977367909595</v>
       </c>
       <c r="C40">
-        <v>1.867058891876685</v>
+        <v>1.867058892420401</v>
       </c>
       <c r="D40">
-        <v>-3.684927881944944</v>
+        <v>-3.684927880871819</v>
       </c>
       <c r="E40">
-        <v>0.0002287674068975049</v>
+        <v>0.0002287674078613659</v>
       </c>
       <c r="F40">
-        <v>0.01277633001628983</v>
+        <v>0.01277632992021027</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1368,22 +1368,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>133.0752581584557</v>
+        <v>133.0752581584556</v>
       </c>
       <c r="B41">
-        <v>-2.994654920257782</v>
+        <v>-2.994654920262419</v>
       </c>
       <c r="C41">
-        <v>0.4290049174982517</v>
+        <v>0.4290049176428619</v>
       </c>
       <c r="D41">
-        <v>-6.980467584663493</v>
+        <v>-6.980467582321305</v>
       </c>
       <c r="E41">
-        <v>2.941992388194277E-12</v>
+        <v>2.941992437244826E-12</v>
       </c>
       <c r="F41">
-        <v>8.560066314111426E-10</v>
+        <v>8.560066456829657E-10</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1393,22 +1393,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>44.74895125916473</v>
+        <v>44.74895125916471</v>
       </c>
       <c r="B42">
-        <v>-2.006740850005107</v>
+        <v>-2.006740850002491</v>
       </c>
       <c r="C42">
-        <v>0.6224458095424327</v>
+        <v>0.6224458098639797</v>
       </c>
       <c r="D42">
-        <v>-3.223960735602488</v>
+        <v>-3.22396073393283</v>
       </c>
       <c r="E42">
-        <v>0.001264307336948489</v>
+        <v>0.001264307344319991</v>
       </c>
       <c r="F42">
-        <v>0.04917473009776514</v>
+        <v>0.04917473038447676</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>26.10666445920848</v>
+        <v>26.10666445920847</v>
       </c>
       <c r="B43">
-        <v>-2.979412136279396</v>
+        <v>-2.979412136279843</v>
       </c>
       <c r="C43">
-        <v>0.846674852366925</v>
+        <v>0.8466748527831934</v>
       </c>
       <c r="D43">
-        <v>-3.518956690340205</v>
+        <v>-3.518956688610634</v>
       </c>
       <c r="E43">
-        <v>0.0004332474282261759</v>
+        <v>0.0004332474310506129</v>
       </c>
       <c r="F43">
-        <v>0.021777520229442</v>
+        <v>0.02177752037141453</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1446,19 +1446,19 @@
         <v>37.41694170913278</v>
       </c>
       <c r="B44">
-        <v>-3.385402720978933</v>
+        <v>-3.385402720979351</v>
       </c>
       <c r="C44">
-        <v>0.7097420981489759</v>
+        <v>0.7097420984921854</v>
       </c>
       <c r="D44">
-        <v>-4.769905476662781</v>
+        <v>-4.76990547435679</v>
       </c>
       <c r="E44">
-        <v>1.843123856694854E-06</v>
+        <v>1.843123877793958E-06</v>
       </c>
       <c r="F44">
-        <v>0.0001977763400836393</v>
+        <v>0.0001977763423476779</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>2036.919468112259</v>
       </c>
       <c r="B45">
-        <v>2.381347865325224</v>
+        <v>2.381347865325395</v>
       </c>
       <c r="C45">
-        <v>0.1473285397935542</v>
+        <v>0.1473285397084432</v>
       </c>
       <c r="D45">
-        <v>16.16352044662979</v>
+        <v>16.16352045596854</v>
       </c>
       <c r="E45">
-        <v>9.120129290541262E-59</v>
+        <v>9.120127908653444E-59</v>
       </c>
       <c r="F45">
-        <v>1.379875561658893E-54</v>
+        <v>1.379875352579266E-54</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1493,22 +1493,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>59.62519179150297</v>
+        <v>59.62519179150298</v>
       </c>
       <c r="B46">
-        <v>3.514802001633792</v>
+        <v>3.514802001633957</v>
       </c>
       <c r="C46">
-        <v>0.564769208622672</v>
+        <v>0.5647692088867975</v>
       </c>
       <c r="D46">
-        <v>6.22343064737098</v>
+        <v>6.223430644460763</v>
       </c>
       <c r="E46">
-        <v>4.863998772132384E-10</v>
+        <v>4.863998862396773E-10</v>
       </c>
       <c r="F46">
-        <v>1.036511287638915E-07</v>
+        <v>1.036511306874129E-07</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1521,19 +1521,19 @@
         <v>281.959241786107</v>
       </c>
       <c r="B47">
-        <v>2.880088237671226</v>
+        <v>2.88008823767172</v>
       </c>
       <c r="C47">
-        <v>0.2850114294113695</v>
+        <v>0.285011429474138</v>
       </c>
       <c r="D47">
-        <v>10.10516751422719</v>
+        <v>10.10516751200344</v>
       </c>
       <c r="E47">
-        <v>5.240593132461185E-24</v>
+        <v>5.240593251355791E-24</v>
       </c>
       <c r="F47">
-        <v>4.664127887890455E-21</v>
+        <v>4.664127993706654E-21</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1543,22 +1543,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>27.43658905943516</v>
+        <v>27.43658905943519</v>
       </c>
       <c r="B48">
-        <v>4.807300714362421</v>
+        <v>4.807300714358519</v>
       </c>
       <c r="C48">
-        <v>1.060222508244381</v>
+        <v>1.060222508604969</v>
       </c>
       <c r="D48">
-        <v>4.534237555777621</v>
+        <v>4.534237554231821</v>
       </c>
       <c r="E48">
-        <v>5.781193457312006E-06</v>
+        <v>5.781193499646645E-06</v>
       </c>
       <c r="F48">
-        <v>0.000553289424565181</v>
+        <v>0.0005532894285023833</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1568,22 +1568,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>243.2520123160039</v>
+        <v>243.252012316004</v>
       </c>
       <c r="B49">
-        <v>3.283481352621223</v>
+        <v>3.283481352622075</v>
       </c>
       <c r="C49">
-        <v>0.3203976696463355</v>
+        <v>0.3203976697251352</v>
       </c>
       <c r="D49">
-        <v>10.24814367796628</v>
+        <v>10.24814367544848</v>
       </c>
       <c r="E49">
-        <v>1.206380980769229E-24</v>
+        <v>1.206381012188282E-24</v>
       </c>
       <c r="F49">
-        <v>1.216836282602562E-21</v>
+        <v>1.216836314293914E-21</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1596,19 +1596,19 @@
         <v>122.7052861582954</v>
       </c>
       <c r="B50">
-        <v>2.186591439792964</v>
+        <v>2.186591439770319</v>
       </c>
       <c r="C50">
-        <v>0.4268476234318688</v>
+        <v>0.4268476235967738</v>
       </c>
       <c r="D50">
-        <v>5.122651081462509</v>
+        <v>5.12265107943041</v>
       </c>
       <c r="E50">
-        <v>3.012695286847324E-07</v>
+        <v>3.012695319326414E-07</v>
       </c>
       <c r="F50">
-        <v>4.101638699869099E-05</v>
+        <v>4.101638749330025E-05</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1618,22 +1618,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>32.86891104378677</v>
+        <v>32.86891104378679</v>
       </c>
       <c r="B51">
-        <v>3.606226914682792</v>
+        <v>3.606226914692416</v>
       </c>
       <c r="C51">
-        <v>0.7895461985113191</v>
+        <v>0.7895461988678996</v>
       </c>
       <c r="D51">
-        <v>4.567467896726365</v>
+        <v>4.567467894675762</v>
       </c>
       <c r="E51">
-        <v>4.936512537793297E-06</v>
+        <v>4.936512586071091E-06</v>
       </c>
       <c r="F51">
-        <v>0.0004881662398484483</v>
+        <v>0.0004881662446225857</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>52.38442597296072</v>
+        <v>52.38442597296073</v>
       </c>
       <c r="B52">
-        <v>3.199375629396934</v>
+        <v>3.199375629395842</v>
       </c>
       <c r="C52">
-        <v>0.624733664641013</v>
+        <v>0.6247336649181587</v>
       </c>
       <c r="D52">
-        <v>5.121183330556345</v>
+        <v>5.121183328282727</v>
       </c>
       <c r="E52">
-        <v>3.036242791707463E-07</v>
+        <v>3.03624282832097E-07</v>
       </c>
       <c r="F52">
-        <v>4.101638699869099E-05</v>
+        <v>4.101638749330025E-05</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1671,19 +1671,19 @@
         <v>98.06864952251209</v>
       </c>
       <c r="B53">
-        <v>2.201511747798213</v>
+        <v>2.20151174778526</v>
       </c>
       <c r="C53">
-        <v>0.5070412891124444</v>
+        <v>0.5070412893052807</v>
       </c>
       <c r="D53">
-        <v>4.341878649866703</v>
+        <v>4.341878648189868</v>
       </c>
       <c r="E53">
-        <v>1.412695567952005E-05</v>
+        <v>1.412695578736257E-05</v>
       </c>
       <c r="F53">
-        <v>0.001167982729131904</v>
+        <v>0.001167982738048064</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1696,19 +1696,19 @@
         <v>9.213496930740945</v>
       </c>
       <c r="B54">
-        <v>6.706414393531414</v>
+        <v>6.706414393529394</v>
       </c>
       <c r="C54">
-        <v>1.962132230269394</v>
+        <v>1.96213223090917</v>
       </c>
       <c r="D54">
-        <v>3.417921733343449</v>
+        <v>3.417921732227965</v>
       </c>
       <c r="E54">
-        <v>0.0006310124969920313</v>
+        <v>0.0006310124995781494</v>
       </c>
       <c r="F54">
-        <v>0.02928594809659336</v>
+        <v>0.02928594821661779</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1718,22 +1718,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>231.5262055287909</v>
+        <v>231.526205528791</v>
       </c>
       <c r="B55">
-        <v>2.43449614244888</v>
+        <v>2.434496142448709</v>
       </c>
       <c r="C55">
-        <v>0.2970843894369044</v>
+        <v>0.2970843895223939</v>
       </c>
       <c r="D55">
-        <v>8.194628290847726</v>
+        <v>8.194628288489051</v>
       </c>
       <c r="E55">
-        <v>2.513687408896044E-16</v>
+        <v>2.513687458185184E-16</v>
       </c>
       <c r="F55">
-        <v>1.152487590805974E-13</v>
+        <v>1.152487613404298E-13</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1746,19 +1746,19 @@
         <v>22.43953371047412</v>
       </c>
       <c r="B56">
-        <v>7.987237607052409</v>
+        <v>7.987237607054984</v>
       </c>
       <c r="C56">
-        <v>1.674482653598277</v>
+        <v>1.67448265389402</v>
       </c>
       <c r="D56">
-        <v>4.769973334682639</v>
+        <v>4.769973333841717</v>
       </c>
       <c r="E56">
-        <v>1.842503077272262E-06</v>
+        <v>1.842503084963949E-06</v>
       </c>
       <c r="F56">
-        <v>0.0001977763400836393</v>
+        <v>0.0001977763423476779</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1771,19 +1771,19 @@
         <v>472.2165216953264</v>
       </c>
       <c r="B57">
-        <v>2.121290873141983</v>
+        <v>2.121290873142052</v>
       </c>
       <c r="C57">
-        <v>0.2706206457758034</v>
+        <v>0.270620645790879</v>
       </c>
       <c r="D57">
-        <v>7.838614334323087</v>
+        <v>7.838614333886672</v>
       </c>
       <c r="E57">
-        <v>4.555453260159751E-15</v>
+        <v>4.555453275989435E-15</v>
       </c>
       <c r="F57">
-        <v>1.86281102233019E-12</v>
+        <v>1.862811028803247E-12</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -1796,19 +1796,19 @@
         <v>391.5176235704284</v>
       </c>
       <c r="B58">
-        <v>3.496836325876888</v>
+        <v>3.496836325877056</v>
       </c>
       <c r="C58">
-        <v>0.2695158759745424</v>
+        <v>0.2695158760060956</v>
       </c>
       <c r="D58">
-        <v>12.97450962112224</v>
+        <v>12.97450961960389</v>
       </c>
       <c r="E58">
-        <v>1.706852276739515E-38</v>
+        <v>1.706852310561681E-38</v>
       </c>
       <c r="F58">
-        <v>5.164934989413774E-35</v>
+        <v>5.164935091759648E-35</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1818,22 +1818,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>56.2509099373325</v>
+        <v>56.25090993733252</v>
       </c>
       <c r="B59">
-        <v>2.682614880041985</v>
+        <v>2.682614880039511</v>
       </c>
       <c r="C59">
-        <v>0.6125082967998717</v>
+        <v>0.6125082970815401</v>
       </c>
       <c r="D59">
-        <v>4.379720069193594</v>
+        <v>4.379720067175494</v>
       </c>
       <c r="E59">
-        <v>1.188318607673387E-05</v>
+        <v>1.188318618678021E-05</v>
       </c>
       <c r="F59">
-        <v>0.000993329311276152</v>
+        <v>0.0009933293204750526</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -1846,19 +1846,19 @@
         <v>220.907296978958</v>
       </c>
       <c r="B60">
-        <v>2.529186071502532</v>
+        <v>2.52918607150253</v>
       </c>
       <c r="C60">
-        <v>0.3108875477489419</v>
+        <v>0.3108875478384382</v>
       </c>
       <c r="D60">
-        <v>8.135372708928772</v>
+        <v>8.135372706586804</v>
       </c>
       <c r="E60">
-        <v>4.106729350697282E-16</v>
+        <v>4.106729430090851E-16</v>
       </c>
       <c r="F60">
-        <v>1.827494561060291E-13</v>
+        <v>1.827494596390428E-13</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -1871,19 +1871,19 @@
         <v>116.0966582696386</v>
       </c>
       <c r="B61">
-        <v>2.196697812997344</v>
+        <v>2.196697812996761</v>
       </c>
       <c r="C61">
-        <v>0.4010769970069241</v>
+        <v>0.4010769971760297</v>
       </c>
       <c r="D61">
-        <v>5.47699775701527</v>
+        <v>5.476997754704557</v>
       </c>
       <c r="E61">
-        <v>4.326026991194471E-08</v>
+        <v>4.326027047663542E-08</v>
       </c>
       <c r="F61">
-        <v>6.661265869676679E-06</v>
+        <v>6.661265897226681E-06</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -1893,22 +1893,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>531.3307887950731</v>
+        <v>531.3307887950732</v>
       </c>
       <c r="B62">
         <v>3.539099180359093</v>
       </c>
       <c r="C62">
-        <v>0.7985861299230426</v>
+        <v>0.7985861299230418</v>
       </c>
       <c r="D62">
-        <v>4.431706296602154</v>
+        <v>4.431706296602158</v>
       </c>
       <c r="E62">
-        <v>9.349030665140559E-06</v>
+        <v>9.349030665140366E-06</v>
       </c>
       <c r="F62">
-        <v>0.0008129358273768773</v>
+        <v>0.0008129358273768605</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -1918,22 +1918,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>2224.096629784239</v>
+        <v>2224.09662978424</v>
       </c>
       <c r="B63">
-        <v>2.762501844226582</v>
+        <v>2.76250184422554</v>
       </c>
       <c r="C63">
-        <v>0.187572730249281</v>
+        <v>0.1875727301701005</v>
       </c>
       <c r="D63">
-        <v>14.72763039998013</v>
+        <v>14.72763040619157</v>
       </c>
       <c r="E63">
-        <v>4.284680002095171E-49</v>
+        <v>4.284679608342295E-49</v>
       </c>
       <c r="F63">
-        <v>1.620680210792498E-45</v>
+        <v>1.620680061855473E-45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -1946,19 +1946,19 @@
         <v>206.4672456675959</v>
       </c>
       <c r="B64">
-        <v>2.665960860173237</v>
+        <v>2.665960860173974</v>
       </c>
       <c r="C64">
-        <v>0.3207854393920151</v>
+        <v>0.3207854394879984</v>
       </c>
       <c r="D64">
-        <v>8.31072901945311</v>
+        <v>8.310729016968727</v>
       </c>
       <c r="E64">
-        <v>9.511590420076063E-17</v>
+        <v>9.511590619228578E-17</v>
       </c>
       <c r="F64">
-        <v>4.962426312267271E-14</v>
+        <v>4.962426416169945E-14</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -1971,19 +1971,19 @@
         <v>487.9558568164775</v>
       </c>
       <c r="B65">
-        <v>2.062991258034396</v>
+        <v>2.0629912580335</v>
       </c>
       <c r="C65">
-        <v>0.248620048887793</v>
+        <v>0.2486200489007739</v>
       </c>
       <c r="D65">
-        <v>8.297767083802091</v>
+        <v>8.297767083365247</v>
       </c>
       <c r="E65">
-        <v>1.060864051009508E-16</v>
+        <v>1.06086405490929E-16</v>
       </c>
       <c r="F65">
-        <v>5.350291030591287E-14</v>
+        <v>5.350291050259185E-14</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -1996,19 +1996,19 @@
         <v>389.1192140317867</v>
       </c>
       <c r="B66">
-        <v>3.295352853457818</v>
+        <v>3.29535285345675</v>
       </c>
       <c r="C66">
-        <v>0.2564733641010276</v>
+        <v>0.2564733641330753</v>
       </c>
       <c r="D66">
-        <v>12.84871380312126</v>
+        <v>12.84871380151158</v>
       </c>
       <c r="E66">
-        <v>8.745218095952572E-38</v>
+        <v>8.745218277906401E-38</v>
       </c>
       <c r="F66">
-        <v>1.890216425596606E-34</v>
+        <v>1.890216464924626E-34</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2021,19 +2021,19 @@
         <v>166.8930713255982</v>
       </c>
       <c r="B67">
-        <v>2.815225004686559</v>
+        <v>2.815225004686495</v>
       </c>
       <c r="C67">
-        <v>0.3543745775307329</v>
+        <v>0.3543745776508204</v>
       </c>
       <c r="D67">
-        <v>7.944207014800353</v>
+        <v>7.944207012108102</v>
       </c>
       <c r="E67">
-        <v>1.954369723209061E-15</v>
+        <v>1.954369765651556E-15</v>
       </c>
       <c r="F67">
-        <v>8.213781642264749E-13</v>
+        <v>8.213781820641125E-13</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>101.4197546401258</v>
       </c>
       <c r="B68">
-        <v>2.122913206432531</v>
+        <v>2.122913206432021</v>
       </c>
       <c r="C68">
-        <v>0.42941238214591</v>
+        <v>0.4294123823328357</v>
       </c>
       <c r="D68">
-        <v>4.943763372224292</v>
+        <v>4.943763370071056</v>
       </c>
       <c r="E68">
-        <v>7.662870685418346E-07</v>
+        <v>7.662870770098219E-07</v>
       </c>
       <c r="F68">
-        <v>9.20152646590314E-05</v>
+        <v>9.201526567586194E-05</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2071,19 +2071,19 @@
         <v>1540.953853164181</v>
       </c>
       <c r="B69">
-        <v>2.608731096754094</v>
+        <v>2.608731096755038</v>
       </c>
       <c r="C69">
-        <v>0.2014430670200268</v>
+        <v>0.2014430669533752</v>
       </c>
       <c r="D69">
-        <v>12.95021534047008</v>
+        <v>12.95021534475961</v>
       </c>
       <c r="E69">
-        <v>2.342959132660839E-38</v>
+        <v>2.342959001741476E-38</v>
       </c>
       <c r="F69">
-        <v>5.908161946193082E-35</v>
+        <v>5.908161616058088E-35</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>57.53787885701774</v>
+        <v>57.53787885701776</v>
       </c>
       <c r="B70">
-        <v>4.757719458007817</v>
+        <v>4.757719458003573</v>
       </c>
       <c r="C70">
-        <v>0.7681653546720827</v>
+        <v>0.7681653549272617</v>
       </c>
       <c r="D70">
-        <v>6.193613691467263</v>
+        <v>6.193613689404263</v>
       </c>
       <c r="E70">
-        <v>5.88002396333114E-10</v>
+        <v>5.880024040330363E-10</v>
       </c>
       <c r="F70">
-        <v>1.235621702294446E-07</v>
+        <v>1.235621718474978E-07</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>637.3244152908514</v>
+        <v>637.3244152908517</v>
       </c>
       <c r="B71">
-        <v>2.489469077734911</v>
+        <v>2.489469077734889</v>
       </c>
       <c r="C71">
-        <v>0.2044195569504398</v>
+        <v>0.2044195569413558</v>
       </c>
       <c r="D71">
-        <v>12.17823340815902</v>
+        <v>12.17823340870008</v>
       </c>
       <c r="E71">
-        <v>4.059803256511711E-34</v>
+        <v>4.05980322958264E-34</v>
       </c>
       <c r="F71">
-        <v>6.142482327102219E-31</v>
+        <v>6.142482286358534E-31</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2146,19 +2146,19 @@
         <v>36.0584208315917</v>
       </c>
       <c r="B72">
-        <v>2.668456778918887</v>
+        <v>2.668456778918957</v>
       </c>
       <c r="C72">
-        <v>0.7147660154298044</v>
+        <v>0.7147660157836306</v>
       </c>
       <c r="D72">
-        <v>3.733329119340244</v>
+        <v>3.733329117492255</v>
       </c>
       <c r="E72">
-        <v>0.0001889654125221055</v>
+        <v>0.0001889654139091684</v>
       </c>
       <c r="F72">
-        <v>0.01070804004291931</v>
+        <v>0.01070804012151954</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2168,22 +2168,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>66.06870726629838</v>
+        <v>66.06870726629839</v>
       </c>
       <c r="B73">
-        <v>4.02562172318551</v>
+        <v>4.025621723184812</v>
       </c>
       <c r="C73">
-        <v>0.6016424813610779</v>
+        <v>0.6016424815843051</v>
       </c>
       <c r="D73">
-        <v>6.69105298894198</v>
+        <v>6.69105298645824</v>
       </c>
       <c r="E73">
-        <v>2.215704077009082E-11</v>
+        <v>2.215704114620771E-11</v>
       </c>
       <c r="F73">
-        <v>5.407032691152807E-09</v>
+        <v>5.407032782937462E-09</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>6112.780875542746</v>
+        <v>6112.780875542745</v>
       </c>
       <c r="B74">
-        <v>2.008766364186682</v>
+        <v>2.00876636418668</v>
       </c>
       <c r="C74">
-        <v>0.4578862447809192</v>
+        <v>0.4578862447809183</v>
       </c>
       <c r="D74">
-        <v>4.387042386800238</v>
+        <v>4.387042386800243</v>
       </c>
       <c r="E74">
-        <v>1.149024043304093E-05</v>
+        <v>1.149024043304069E-05</v>
       </c>
       <c r="F74">
-        <v>0.0009766704368084787</v>
+        <v>0.000976670436808459</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2218,22 +2218,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>3484.852481581971</v>
+        <v>3484.852481581972</v>
       </c>
       <c r="B75">
-        <v>2.395917470650539</v>
+        <v>2.395917470650867</v>
       </c>
       <c r="C75">
-        <v>0.1491525231956763</v>
+        <v>0.1491525230924564</v>
       </c>
       <c r="D75">
-        <v>16.06353965267678</v>
+        <v>16.06353966379563</v>
       </c>
       <c r="E75">
-        <v>4.595604522852159E-58</v>
+        <v>4.595603698883316E-58</v>
       </c>
       <c r="F75">
-        <v>3.476574821537658E-54</v>
+        <v>3.476574198205228E-54</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2246,19 +2246,19 @@
         <v>374.8947037592645</v>
       </c>
       <c r="B76">
-        <v>2.062982421587847</v>
+        <v>2.062982421585114</v>
       </c>
       <c r="C76">
-        <v>0.2740945135503995</v>
+        <v>0.274094513587881</v>
       </c>
       <c r="D76">
-        <v>7.526536722189854</v>
+        <v>7.526536721150658</v>
       </c>
       <c r="E76">
-        <v>5.210383089137148E-14</v>
+        <v>5.210383130586409E-14</v>
       </c>
       <c r="F76">
-        <v>1.751846580858779E-11</v>
+        <v>1.751846594794942E-11</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2268,22 +2268,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>96.80721033096209</v>
+        <v>96.80721033096212</v>
       </c>
       <c r="B77">
-        <v>2.233004968787009</v>
+        <v>2.233004968787342</v>
       </c>
       <c r="C77">
-        <v>0.4344068312080649</v>
+        <v>0.4344068314018738</v>
       </c>
       <c r="D77">
-        <v>5.140354175778329</v>
+        <v>5.140354173485748</v>
       </c>
       <c r="E77">
-        <v>2.742210758765256E-07</v>
+        <v>2.742210792225638E-07</v>
       </c>
       <c r="F77">
-        <v>3.80638979634113E-05</v>
+        <v>3.806389842786596E-05</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2293,22 +2293,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>20.78903158545554</v>
+        <v>20.78903158545555</v>
       </c>
       <c r="B78">
-        <v>4.377179735618593</v>
+        <v>4.377179735631193</v>
       </c>
       <c r="C78">
-        <v>1.162208077840796</v>
+        <v>1.162208078332466</v>
       </c>
       <c r="D78">
-        <v>3.766261669554664</v>
+        <v>3.766261667972195</v>
       </c>
       <c r="E78">
-        <v>0.0001657101179093417</v>
+        <v>0.000165710118959128</v>
       </c>
       <c r="F78">
-        <v>0.009717806527009071</v>
+        <v>0.009717806588572121</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
